--- a/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>63.7</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>63.7</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>63.7</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>63.7</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>64.3</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>63.7</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>94.90000000000001</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>63.7</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -6128,7 +6128,7 @@
         <v>63.7</v>
       </c>
       <c r="R21" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6408,7 +6408,7 @@
         <v>32</v>
       </c>
       <c r="R22" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S22" t="n">
         <v>64.3</v>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>32</v>
       </c>
       <c r="R24" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S24" t="n">
         <v>86.40000000000001</v>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>32</v>
       </c>
       <c r="R26" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S26" t="n">
         <v>96.59999999999999</v>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>32</v>
       </c>
       <c r="R27" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S27" t="n">
         <v>93.2</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8088,7 +8088,7 @@
         <v>32</v>
       </c>
       <c r="R28" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8648,7 +8648,7 @@
         <v>63.7</v>
       </c>
       <c r="R30" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S30" t="n">
         <v>44.8</v>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>63.7</v>
       </c>
       <c r="R31" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S31" t="n">
         <v>52.4</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>32</v>
       </c>
       <c r="R35" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S35" t="n">
         <v>44.8</v>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>30.7</v>
       </c>
       <c r="R36" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S36" t="n">
         <v>52.4</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
@@ -11190,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>63.7</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>63.7</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>63.7</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -13365,7 +13365,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>63.7</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
         <v>64.3</v>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>63.7</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>96.59999999999999</v>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>94.90000000000001</v>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>63.7</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -16534,7 +16534,7 @@
         <v>63.7</v>
       </c>
       <c r="R21" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
